--- a/output/pdf_financials_xlsx/DOSE.xlsx
+++ b/output/pdf_financials_xlsx/DOSE.xlsx
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5.404265</v>
+        <v>-5.404265</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.389667</v>
+        <v>-3.389667</v>
       </c>
     </row>
     <row r="17">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5.404265</v>
+        <v>-5.404265</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.389667</v>
+        <v>-3.389667</v>
       </c>
     </row>
     <row r="21">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>5.404265</v>
+        <v>-5.404265</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3.389667</v>
+        <v>-3.389667</v>
       </c>
     </row>
     <row r="24">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-135.106625</v>
+        <v>135.106625</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-112.9889</v>
+        <v>112.9889</v>
       </c>
     </row>
     <row r="27">
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5.404265</v>
+        <v>-5.404265</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.389667</v>
+        <v>-3.389667</v>
       </c>
     </row>
     <row r="28">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5.645019</v>
+        <v>-5.163511</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.903109</v>
+        <v>-2.876225</v>
       </c>
     </row>
     <row r="30">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>270.7214642792742</v>
+        <v>-247.6295046557221</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>140.7381859668151</v>
+        <v>-103.7108338333372</v>
       </c>
     </row>
     <row r="31">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>259.1754844674982</v>
+        <v>-259.1754844674982</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>122.2245099000762</v>
+        <v>-122.2245099000762</v>
       </c>
     </row>
     <row r="33">
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>5.244026</v>
+        <v>9.467979</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>6.647315</v>
+        <v>11.118877</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>7.0049</v>
+        <v>11.515399</v>
       </c>
     </row>
     <row r="93">
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="C99" s="3" t="n">
-        <v>5.404265</v>
+        <v>-5.404265</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>3.389667</v>
+        <v>-3.389667</v>
       </c>
     </row>
     <row r="100">
@@ -3278,7 +3278,11 @@
           <t>Warrant reserve 17</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -3650,7 +3654,11 @@
           <t>Warrant reserve 16</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>4.223953</v>
       </c>
@@ -5898,10 +5906,10 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>5.404265</v>
+        <v>-5.404265</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>3.389667</v>
+        <v>-3.389667</v>
       </c>
     </row>
     <row r="105">

--- a/output/pdf_financials_xlsx/DOSE.xlsx
+++ b/output/pdf_financials_xlsx/DOSE.xlsx
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>0.770919</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -4293,7 +4293,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -5277,7 +5281,11 @@
           <t>Issuance of common shares, net of issue costs 14</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DOSE.xlsx
+++ b/output/pdf_financials_xlsx/DOSE.xlsx
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>1.121128</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.938008</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>2.149955</v>
       </c>
     </row>
     <row r="65">
@@ -1552,13 +1552,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>1.468317</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>2.2927</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>2.527772</v>
       </c>
     </row>
     <row r="68">
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.187422</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.535242</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.589585</v>
       </c>
     </row>
     <row r="111">
@@ -3782,7 +3782,11 @@
           <t>Accretion expense 13</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -4907,7 +4911,11 @@
           <t>Accretion expense 11,12</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
         <v>0.187422</v>
       </c>
